--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>824.67</v>
+        <v>820.4299999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>923.9</v>
+        <v>914.23</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>965.4299999999999</v>
+        <v>955.3200000000001</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3971</v>
+        <v>3926.76</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1277.25</v>
+        <v>1270.25</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>905.8200000000001</v>
+        <v>904.67</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>748.5</v>
+        <v>747.55</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25155.14</v>
+        <v>25237.88</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>769.22</v>
+        <v>782.5</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1758.12</v>
+        <v>1767.2</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>799.74</v>
+        <v>805.38</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4551.33</v>
+        <v>4493.52</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1208.03</v>
+        <v>1196.01</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5566.18</v>
+        <v>5510.8</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2016.3</v>
+        <v>1996.24</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5102.32</v>
+        <v>5051.56</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2474.4</v>
+        <v>2449.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1065.09</v>
+        <v>1061.28</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1491.26</v>
+        <v>1488.03</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1860.02</v>
+        <v>1855.99</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>794.92</v>
+        <v>788.1900000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1543.09</v>
+        <v>1530.02</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1179.5</v>
+        <v>1184.85</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1100.89</v>
+        <v>1112.7</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1284.74</v>
+        <v>1301.25</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3272.03</v>
+        <v>3195.49</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2046.77</v>
+        <v>2017.43</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>938.25</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1861.01</v>
+        <v>1834.19</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>921.54</v>
+        <v>908.26</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>834.45</v>
+        <v>822.42</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1442.2</v>
+        <v>1421.42</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>801.77</v>
+        <v>791.41</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3618.2</v>
+        <v>3618.22</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2431.25</v>
+        <v>2429.59</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1103.89</v>
+        <v>1100.1</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1642.69</v>
+        <v>1637.06</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5974.81</v>
+        <v>5943.25</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>831.48</v>
+        <v>827.09</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>926.9400000000001</v>
+        <v>939.4299999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1025.81</v>
+        <v>1050.75</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>883.11</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1388.69</v>
+        <v>1423.79</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>869.11</v>
+        <v>891.08</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>818.49</v>
+        <v>843.3099999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>896.5700000000001</v>
+        <v>923.76</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1535.26</v>
+        <v>1529.79</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1020.42</v>
+        <v>1025.69</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>812.41</v>
+        <v>814.64</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1592.52</v>
+        <v>1603.61</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4523.44</v>
+        <v>4563.73</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1187.21</v>
+        <v>1185.18</v>
       </c>
     </row>
     <row r="54">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>849.5</v>
+        <v>843.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-1919-CM26</t>
+          <t>1057402-1920-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4066.89</v>
+        <v>2285.46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-1920-CM26</t>
+          <t>1057402-1919-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2301.95</v>
+        <v>4037.75</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3685.46</v>
+        <v>3680.04</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>811.5</v>
+        <v>807.08</v>
       </c>
     </row>
     <row r="59">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>822.49</v>
+        <v>817.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3130-5423-CM26</t>
+          <t>1057402-2301-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora BBC Chile S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1051.92</v>
+        <v>813.9299999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-2301-CM26</t>
+          <t>1057402-2304-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>813.15</v>
+        <v>829.09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-2304-CM26</t>
+          <t>1057402-2316-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>828.29</v>
+        <v>941.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-2316-CM26</t>
+          <t>3130-5423-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Importadora y Comercializadora BBC Chile S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>940.45</v>
+        <v>1052.94</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4185.11</v>
+        <v>4369.93</v>
       </c>
     </row>
     <row r="65">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8631.780000000001</v>
+        <v>8882.51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>874750-78-CM26</t>
+          <t>3130-5458-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>768.88</v>
+        <v>886.26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3130-5458-CM26</t>
+          <t>874750-78-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>882.78</v>
+        <v>771.91</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3185.18</v>
+        <v>3237.68</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1326.69</v>
+        <v>1348.55</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6622.09</v>
+        <v>6731.23</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2403.17</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>785.97</v>
+        <v>775.85</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1334</v>
+        <v>1324.59</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3295.38</v>
+        <v>3295.21</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4223.67</v>
+        <v>4223.46</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>16743.96</v>
+        <v>16669.09</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1120.8</v>
+        <v>1115.79</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1599.02</v>
+        <v>1605.62</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1331.7</v>
+        <v>1337.2</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>886.51</v>
+        <v>890.17</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>782.75</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>997.23</v>
+        <v>994.48</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4185.11</v>
+        <v>4161.07</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>14148.46</v>
+        <v>14067.19</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2092.55</v>
+        <v>2080.53</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>921.4400000000001</v>
+        <v>908.11</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1006.91</v>
+        <v>983.48</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2544.64</v>
+        <v>2463.5</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3710.94</v>
+        <v>3611.57</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1338.59</v>
+        <v>1342.49</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>932.66</v>
+        <v>935.38</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>872.0700000000001</v>
+        <v>870.61</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>959.25</v>
+        <v>971.0599999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4479.63</v>
+        <v>4539.27</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2544.64</v>
+        <v>2578.52</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1427.37</v>
+        <v>1446.37</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5627.23</v>
+        <v>5765.71</v>
       </c>
     </row>
     <row r="98">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>786.37</v>
+        <v>805.73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1540-969-CM26</t>
+          <t>1540-970-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6540.53</v>
+        <v>806.62</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1540-970-CM26</t>
+          <t>1540-969-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>787.25</v>
+        <v>6701.49</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>873.22</v>
+        <v>894.71</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1505.58</v>
+        <v>1534.06</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>848.21</v>
+        <v>857.86</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1848.84</v>
+        <v>1869.87</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1080.62</v>
+        <v>1090.36</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4482.07</v>
+        <v>4500.65</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1789.39</v>
+        <v>1781.71</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>844.5700000000001</v>
+        <v>840.9400000000001</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4347.1</v>
+        <v>4328.42</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>816.41</v>
+        <v>812.9</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2315.21</v>
+        <v>2301.33</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1869.24</v>
+        <v>1858.04</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>11215.44</v>
+        <v>11148.22</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1140.1</v>
+        <v>1130.38</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>834.78</v>
+        <v>837.9400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>864.9299999999999</v>
+        <v>868.21</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>842.66</v>
+        <v>838.96</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1606.88</v>
+        <v>1589.4</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1378.73</v>
+        <v>1375.6</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1509.97</v>
+        <v>1506.55</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1185.52</v>
+        <v>1191.34</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1157.6</v>
+        <v>1161.44</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>825.65</v>
+        <v>828.39</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1710.16</v>
+        <v>1715.6</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>809.96</v>
+        <v>819.46</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>885.0700000000001</v>
+        <v>895.45</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1158.91</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>821.98</v>
+        <v>831.62</v>
       </c>
     </row>
     <row r="129">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1877.11</v>
+        <v>1896.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057402-6044-CM26</t>
+          <t>1057402-6043-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>830.76</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057402-6041-CM26</t>
+          <t>1057402-6044-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>946.85</v>
+        <v>839.2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1057402-6043-CM26</t>
+          <t>1057402-6041-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>832.72</v>
+        <v>956.48</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>853.59</v>
+        <v>862.27</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>918.14</v>
+        <v>926.75</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1151.26</v>
+        <v>1162.06</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>936.92</v>
+        <v>929.8099999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>841.47</v>
+        <v>829.91</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4923.69</v>
+        <v>4856.03</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2057.31</v>
+        <v>2029.04</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3561.37</v>
+        <v>3539.29</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2492.27</v>
+        <v>2503.59</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6753.64</v>
+        <v>6784.31</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>908.92</v>
+        <v>913.04</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1048.61</v>
+        <v>1053.37</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11642.02</v>
+        <v>11694.9</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2642.07</v>
+        <v>2692.3</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1024.31</v>
+        <v>1031.38</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1795.44</v>
+        <v>1800.99</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1006.95</v>
+        <v>1010.06</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>11489.18</v>
+        <v>11458.79</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7991.08</v>
+        <v>7884.64</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2226.53</v>
+        <v>2193.54</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>852.27</v>
+        <v>839.65</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>893.86</v>
+        <v>875.49</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>797.62</v>
+        <v>801.6799999999999</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5456.49</v>
+        <v>5477.73</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>18049.98</v>
+        <v>18088.45</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3455.84</v>
+        <v>3478.37</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7234.67</v>
+        <v>7281.84</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2465.81</v>
+        <v>2481.88</v>
       </c>
     </row>
     <row r="161">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>928.84</v>
+        <v>935.34</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1057402-7627-CM26</t>
+          <t>1540-1639-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>801.6799999999999</v>
+        <v>759.17</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1540-1639-CM26</t>
+          <t>1057402-7627-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>761.58</v>
+        <v>799.15</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>869.02</v>
+        <v>867.13</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2198.57</v>
+        <v>2194.16</v>
       </c>
     </row>
     <row r="166">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>802.09</v>
+        <v>797.45</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1540-1728-CM26</t>
+          <t>1540-1729-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2703.47</v>
+        <v>873.63</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1540-1727-CM26</t>
+          <t>1540-1724-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>851.63</v>
+        <v>887.88</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1540-1729-CM26</t>
+          <t>1540-1725-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>887.86</v>
+        <v>852.3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1540-1725-CM26</t>
+          <t>1540-1726-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>866.1799999999999</v>
+        <v>854.01</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1540-1724-CM26</t>
+          <t>1540-1727-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>902.35</v>
+        <v>837.97</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1540-1726-CM26</t>
+          <t>1540-1728-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>867.92</v>
+        <v>2660.12</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,129 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1035.37</v>
+        <v>1023.32</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1057402-8704-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>1325.78</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1057402-9247-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>COMERCIAL LBF LIMITADA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>1965.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057402-37399-CM25</t>
+          <t>3130-43-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>820.4299999999999</v>
+        <v>726.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1239966-440-CM25</t>
+          <t>3130-241-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>914.23</v>
+        <v>808.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3130-4150-CM25</t>
+          <t>3130-1511-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>955.3200000000001</v>
+        <v>1273.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3130-4156-CM25</t>
+          <t>1057402-37399-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3926.76</v>
+        <v>820.4299999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3130-4158-CM25</t>
+          <t>1239966-440-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1270.25</v>
+        <v>914.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>874750-482-CM25</t>
+          <t>3130-4150-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>904.67</v>
+        <v>955.3200000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>874750-483-CM25</t>
+          <t>3130-4156-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>747.55</v>
+        <v>3926.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1237328-672-CM25</t>
+          <t>3130-4158-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>25237.88</v>
+        <v>1270.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3130-4203-CM25</t>
+          <t>874750-482-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>782.5</v>
+        <v>904.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057402-43269-CM25</t>
+          <t>874750-483-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PULSAR MEDICAL</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1767.2</v>
+        <v>747.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057402-43245-CM25</t>
+          <t>1237328-672-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>805.38</v>
+        <v>25237.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3130-4426-CM25</t>
+          <t>3130-4203-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4493.52</v>
+        <v>782.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1237328-702-CM25</t>
+          <t>1057402-43269-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>PULSAR MEDICAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1196.01</v>
+        <v>1767.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1237328-703-CM25</t>
+          <t>1057402-43245-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5510.8</v>
+        <v>805.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1237328-704-CM25</t>
+          <t>3130-4426-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1996.24</v>
+        <v>4493.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1237328-705-CM25</t>
+          <t>1237328-703-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5051.56</v>
+        <v>5510.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3130-4447-CM25</t>
+          <t>1237328-704-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora BBC Chile S.A.</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2449.78</v>
+        <v>1996.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1057402-43715-CM25</t>
+          <t>1237328-705-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA FASTMED  SPA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.994.349-8</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1061.28</v>
+        <v>5051.56</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1237328-713-CM25</t>
+          <t>3130-4447-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>Importadora y Comercializadora BBC Chile S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1488.03</v>
+        <v>2449.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1237328-718-CM25</t>
+          <t>1237328-702-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1855.99</v>
+        <v>1196.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3130-4486-CM25</t>
+          <t>1057402-43715-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>DISTRIBUIDORA FASTMED  SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>76.994.349-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>788.1900000000001</v>
+        <v>1061.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057402-43849-CM25</t>
+          <t>1237328-713-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PULSAR MEDICAL</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1530.02</v>
+        <v>1488.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1239966-515-CM25</t>
+          <t>1237328-718-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1184.85</v>
+        <v>1855.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1540-16710-CM25</t>
+          <t>1057402-43849-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>PULSAR MEDICAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1112.7</v>
+        <v>1530.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057402-43850-CM25</t>
+          <t>3130-4486-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1301.25</v>
+        <v>788.1900000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057402-44612-CM25</t>
+          <t>1239966-515-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3195.49</v>
+        <v>1184.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057402-156-CM26</t>
+          <t>1540-16710-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2017.43</v>
+        <v>1112.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057402-165-CM26</t>
+          <t>1057402-43850-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>924.8</v>
+        <v>1301.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057402-242-CM26</t>
+          <t>1057402-44612-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PULSAR MEDICAL</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1834.19</v>
+        <v>3195.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057402-286-CM26</t>
+          <t>1057402-156-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>908.26</v>
+        <v>2017.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057402-44949-CM25</t>
+          <t>1057402-165-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>822.42</v>
+        <v>924.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057402-213-CM26</t>
+          <t>1057402-286-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MEDICINA TECNICA LTDA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.297.510-2</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1421.42</v>
+        <v>908.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3130-5164-CM26</t>
+          <t>1057402-242-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PTM EMERGENCIA</t>
+          <t>PULSAR MEDICAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.612.187-K</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>791.41</v>
+        <v>1834.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057402-499-CM26</t>
+          <t>1057402-44949-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3618.22</v>
+        <v>822.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3130-5195-CM26</t>
+          <t>1057402-213-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MEDICINA TECNICA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>78.297.510-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2429.59</v>
+        <v>1421.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057402-611-CM26</t>
+          <t>3130-5164-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA FASTMED  SPA</t>
+          <t>PTM EMERGENCIA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.994.349-8</t>
+          <t>76.612.187-K</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1100.1</v>
+        <v>791.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3130-5203-CM26</t>
+          <t>1057402-499-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1637.06</v>
+        <v>3618.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-622-CM26</t>
+          <t>3130-5195-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5943.25</v>
+        <v>2429.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-639-CM26</t>
+          <t>1057402-611-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DISTRIBUIDORA FASTMED  SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.994.349-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>827.09</v>
+        <v>1100.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-805-CM26</t>
+          <t>3130-5203-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>939.4299999999999</v>
+        <v>1637.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3130-5267-CM26</t>
+          <t>1057402-639-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora BBC Chile S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1050.75</v>
+        <v>827.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>874750-27-CM26</t>
+          <t>1057402-622-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>905.4400000000001</v>
+        <v>5943.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3130-5281-CM26</t>
+          <t>1057402-805-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1423.79</v>
+        <v>939.4299999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057402-1177-CM26</t>
+          <t>3130-5267-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Importadora y Comercializadora BBC Chile S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>891.08</v>
+        <v>1050.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-1023-CM26</t>
+          <t>1057402-1177-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>843.3099999999999</v>
+        <v>891.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057402-1110-CM26</t>
+          <t>3130-5281-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>923.76</v>
+        <v>1423.79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057402-1214-CM26</t>
+          <t>874750-27-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1529.79</v>
+        <v>905.4400000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1540-358-CM26</t>
+          <t>1057402-1023-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1025.69</v>
+        <v>843.3099999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057402-1521-CM26</t>
+          <t>1057402-1110-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>814.64</v>
+        <v>923.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057402-1685-CM26</t>
+          <t>1057402-1214-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CODIMED CHILE LTDA.</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.124.770-7</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1603.61</v>
+        <v>1529.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057402-1697-CM26</t>
+          <t>1540-358-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4563.73</v>
+        <v>1025.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3130-5385-CM26</t>
+          <t>1057402-1521-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1185.18</v>
+        <v>814.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057402-1921-CM26</t>
+          <t>1057402-1685-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>CODIMED CHILE LTDA.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>78.124.770-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>843.41</v>
+        <v>1603.61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-1920-CM26</t>
+          <t>1057402-1697-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2285.46</v>
+        <v>4563.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-1919-CM26</t>
+          <t>3130-5385-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4037.75</v>
+        <v>1185.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-1973-CM26</t>
+          <t>1057402-1919-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3680.04</v>
+        <v>4037.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-2070-CM26</t>
+          <t>1057402-1920-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>807.08</v>
+        <v>2285.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-2044-CM26</t>
+          <t>1057402-1921-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>817.64</v>
+        <v>843.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-2301-CM26</t>
+          <t>1057402-1973-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>813.9299999999999</v>
+        <v>3680.04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-2304-CM26</t>
+          <t>1057402-2070-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>829.09</v>
+        <v>807.08</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-2316-CM26</t>
+          <t>1057402-2044-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>941.36</v>
+        <v>817.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3130-5423-CM26</t>
+          <t>1057402-2301-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora BBC Chile S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1052.94</v>
+        <v>813.9299999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057402-2391-CM26</t>
+          <t>1057402-2304-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4369.93</v>
+        <v>829.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057402-2450-CM26</t>
+          <t>1057402-2316-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8882.51</v>
+        <v>941.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3130-5458-CM26</t>
+          <t>3130-5423-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Importadora y Comercializadora BBC Chile S.A.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>886.26</v>
+        <v>1052.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>874750-78-CM26</t>
+          <t>1057402-2391-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,22 +4494,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>771.91</v>
+        <v>4369.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>874750-79-CM26</t>
+          <t>1057402-2450-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3237.68</v>
+        <v>8882.51</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>874750-80-CM26</t>
+          <t>874750-78-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1348.55</v>
+        <v>771.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>874750-81-CM26</t>
+          <t>3130-5458-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6731.23</v>
+        <v>886.26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>874750-82-CM26</t>
+          <t>874750-79-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2372.23</v>
+        <v>3237.68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057402-2677-CM26</t>
+          <t>874750-80-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>775.85</v>
+        <v>1348.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1239966-78-CM26</t>
+          <t>874750-81-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1324.59</v>
+        <v>6731.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057402-2470-CM26</t>
+          <t>874750-82-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3295.21</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>855-35-CM26</t>
+          <t>1057402-2677-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4223.46</v>
+        <v>775.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1237328-88-CM26</t>
+          <t>1239966-78-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>16669.09</v>
+        <v>1324.59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057402-2985-CM26</t>
+          <t>855-35-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1115.79</v>
+        <v>4223.46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1540-694-CM26</t>
+          <t>1057402-2470-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1605.62</v>
+        <v>3295.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1540-695-CM26</t>
+          <t>1057402-2985-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1337.2</v>
+        <v>1115.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1540-697-CM26</t>
+          <t>1237328-88-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>890.17</v>
+        <v>16669.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1540-698-CM26</t>
+          <t>1540-694-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.116.604-2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>785.98</v>
+        <v>1605.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1540-700-CM26</t>
+          <t>1540-695-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>994.48</v>
+        <v>1337.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057402-2988-CM26</t>
+          <t>1540-697-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4161.07</v>
+        <v>890.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057402-3158-CM26</t>
+          <t>1540-698-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>14067.19</v>
+        <v>785.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057402-3225-CM26</t>
+          <t>1540-700-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2080.53</v>
+        <v>994.48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3130-5564-CM26</t>
+          <t>1057402-3225-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>908.11</v>
+        <v>2080.53</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3130-5579-CM26</t>
+          <t>1057402-2988-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>983.48</v>
+        <v>4161.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057402-3582-CM26</t>
+          <t>1057402-3158-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2463.5</v>
+        <v>14067.19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3130-5640-CM26</t>
+          <t>3130-5564-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3611.57</v>
+        <v>908.11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3130-5654-CM26</t>
+          <t>3130-5579-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1342.49</v>
+        <v>983.48</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3130-5658-CM26</t>
+          <t>1057402-3582-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>935.38</v>
+        <v>2463.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057402-3704-CM26</t>
+          <t>3130-5640-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>870.61</v>
+        <v>3611.57</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057402-4049-CM26</t>
+          <t>3130-5654-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>971.0599999999999</v>
+        <v>1342.49</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057402-3770-CM26</t>
+          <t>3130-5658-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4539.27</v>
+        <v>935.38</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057402-3946-CM26</t>
+          <t>1057402-3704-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2578.52</v>
+        <v>870.61</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>902977-10-CM26</t>
+          <t>1057402-4049-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1446.37</v>
+        <v>971.0599999999999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1237328-152-CM26</t>
+          <t>1057402-3770-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5765.71</v>
+        <v>4539.27</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1540-972-CM26</t>
+          <t>1057402-3946-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>805.73</v>
+        <v>2578.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1540-970-CM26</t>
+          <t>902977-10-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>806.62</v>
+        <v>1446.37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1540-969-CM26</t>
+          <t>1237328-152-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>6701.49</v>
+        <v>5765.71</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1540-971-CM26</t>
+          <t>1540-972-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>894.71</v>
+        <v>805.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1540-976-CM26</t>
+          <t>1540-969-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1534.06</v>
+        <v>6701.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1057402-4313-CM26</t>
+          <t>1540-970-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>857.86</v>
+        <v>806.62</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3130-5754-CM26</t>
+          <t>1540-971-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1869.87</v>
+        <v>894.71</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3130-5757-CM26</t>
+          <t>1540-976-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1090.36</v>
+        <v>1534.06</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1057402-4725-CM26</t>
+          <t>1057402-4313-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4500.65</v>
+        <v>857.86</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3130-5797-CM26</t>
+          <t>3130-5754-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1781.71</v>
+        <v>1869.87</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1057402-4519-CM26</t>
+          <t>3130-5757-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>840.9400000000001</v>
+        <v>1090.36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1057402-4516-CM26</t>
+          <t>1057402-4725-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4328.42</v>
+        <v>4500.65</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1057402-4518-CM26</t>
+          <t>3130-5797-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>812.9</v>
+        <v>1781.71</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057402-4735-CM26</t>
+          <t>1057402-4519-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2301.33</v>
+        <v>840.9400000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057402-4790-CM26</t>
+          <t>1057402-4516-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1858.04</v>
+        <v>4328.42</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1057402-4792-CM26</t>
+          <t>1057402-4518-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>11148.22</v>
+        <v>812.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1239966-163-CM26</t>
+          <t>1057402-4735-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1130.38</v>
+        <v>2301.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3130-5875-CM26</t>
+          <t>1057402-4790-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>837.9400000000001</v>
+        <v>1858.04</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3130-5876-CM26</t>
+          <t>1057402-4792-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>868.21</v>
+        <v>11148.22</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057402-5477-CM26</t>
+          <t>1239966-163-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>838.96</v>
+        <v>1130.38</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1540-1191-CM26</t>
+          <t>3130-5875-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1589.4</v>
+        <v>837.9400000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1540-1202-CM26</t>
+          <t>3130-5876-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1375.6</v>
+        <v>868.21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1540-1198-CM26</t>
+          <t>1057402-5477-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1506.55</v>
+        <v>838.96</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3130-5949-CM26</t>
+          <t>1540-1191-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>PULSAR MEDICAL</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.923.737-2</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1191.34</v>
+        <v>1589.4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057402-5535-CM26</t>
+          <t>1540-1202-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>59.077.290-9</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1161.44</v>
+        <v>1375.6</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057402-5538-CM26</t>
+          <t>1540-1198-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>828.39</v>
+        <v>1506.55</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1239966-195-CM26</t>
+          <t>3130-5949-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,22 +7971,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>PULSAR MEDICAL</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.923.737-2</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1715.6</v>
+        <v>1191.34</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057402-5090-CM26</t>
+          <t>1057402-5535-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>819.46</v>
+        <v>1161.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057402-5243-CM26</t>
+          <t>1057402-5538-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>895.45</v>
+        <v>828.39</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057402-5351-CM26</t>
+          <t>1239966-195-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8149,27 +8149,27 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Articulos Medicos y Quirurgicos Chile S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.209.836-9</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1172.51</v>
+        <v>1715.6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057402-5867-CM26</t>
+          <t>1057402-5090-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NIPRO MEDICAL CORPORATION (AGENCIA EN CHILE)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>59.077.290-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>831.62</v>
+        <v>819.46</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1237328-326-CM26</t>
+          <t>1057402-5243-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1896.2</v>
+        <v>895.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057402-6043-CM26</t>
+          <t>1057402-5351-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>Articulos Medicos y Quirurgicos Chile S.A.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>76.209.836-9</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>841.1900000000001</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057402-6044-CM26</t>
+          <t>1057402-5867-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>839.2</v>
+        <v>831.62</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1057402-6041-CM26</t>
+          <t>1237328-326-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>956.48</v>
+        <v>1896.2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1057402-6040-CM26</t>
+          <t>1057402-6044-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>862.27</v>
+        <v>839.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3130-6000-CM26</t>
+          <t>1057402-6043-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>926.75</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3130-6001-CM26</t>
+          <t>1057402-6041-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1162.06</v>
+        <v>956.48</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057402-6115-CM26</t>
+          <t>1057402-6040-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>929.8099999999999</v>
+        <v>862.27</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2354-188-CM26</t>
+          <t>3130-6000-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,22 +8764,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>829.91</v>
+        <v>926.75</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057402-6211-CM26</t>
+          <t>3130-6001-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4856.03</v>
+        <v>1162.06</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3130-6060-CM26</t>
+          <t>1057402-6115-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Importadora y Comercializadora BBC Chile S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.054.237-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2029.04</v>
+        <v>929.8099999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057402-6293-CM26</t>
+          <t>2354-188-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3539.29</v>
+        <v>829.91</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057402-6432-CM26</t>
+          <t>1057402-6211-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2503.59</v>
+        <v>4856.03</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1057402-6431-CM26</t>
+          <t>3130-6060-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>Importadora y Comercializadora BBC Chile S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>76.054.237-7</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6784.31</v>
+        <v>2029.04</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1057402-6429-CM26</t>
+          <t>1057402-6293-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>913.04</v>
+        <v>3539.29</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057402-6384-CM26</t>
+          <t>1057402-6432-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1053.37</v>
+        <v>2503.59</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057402-6430-CM26</t>
+          <t>1057402-6431-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>59.106.780-k</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11694.9</v>
+        <v>6784.31</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3130-6131-CM26</t>
+          <t>1057402-6384-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2692.3</v>
+        <v>1053.37</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1057402-6513-CM26</t>
+          <t>1057402-6429-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA FASTMED  SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.994.349-8</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1031.38</v>
+        <v>913.04</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1057402-6681-CM26</t>
+          <t>1057402-6430-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1800.99</v>
+        <v>11694.9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3130-6138-CM26</t>
+          <t>3130-6131-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1010.06</v>
+        <v>2692.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1057402-6702-CM26</t>
+          <t>1057402-6513-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>DISTRIBUIDORA FASTMED  SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>76.994.349-8</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>11458.79</v>
+        <v>1031.38</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1057402-6750-CM26</t>
+          <t>1057402-6681-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL A M W S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.714.930-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7884.64</v>
+        <v>1800.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>874750-207-CM26</t>
+          <t>3130-6138-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,22 +9679,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2193.54</v>
+        <v>1010.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1057402-6791-CM26</t>
+          <t>1057402-6702-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>839.65</v>
+        <v>11458.79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>874750-211-CM26</t>
+          <t>1057402-6750-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,22 +9801,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>SOC COMERCIAL A M W S.A.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>77.714.930-k</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>875.49</v>
+        <v>7884.64</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057402-7030-CM26</t>
+          <t>874750-207-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9857,27 +9857,27 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>801.6799999999999</v>
+        <v>2193.54</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1057402-7215-CM26</t>
+          <t>1057402-6791-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5477.73</v>
+        <v>839.65</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1540-1566-CM26</t>
+          <t>874750-211-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9979,27 +9979,27 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>18088.45</v>
+        <v>875.49</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1057402-7326-CM26</t>
+          <t>1057402-7030-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3478.37</v>
+        <v>801.6799999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>874750-238-CM26</t>
+          <t>1057402-7215-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,22 +10106,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7281.84</v>
+        <v>5477.73</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>874750-241-CM26</t>
+          <t>1540-1566-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2481.88</v>
+        <v>18088.45</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>874750-240-CM26</t>
+          <t>1057402-7326-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>935.34</v>
+        <v>3478.37</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1540-1639-CM26</t>
+          <t>874750-238-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,22 +10289,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>759.17</v>
+        <v>7281.84</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1057402-7627-CM26</t>
+          <t>874750-241-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>799.15</v>
+        <v>2481.88</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3130-6303-CM26</t>
+          <t>874750-240-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,22 +10411,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>867.13</v>
+        <v>935.34</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1239966-298-CM26</t>
+          <t>1540-1639-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,22 +10472,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2194.16</v>
+        <v>759.17</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3263-33-CM26</t>
+          <t>1057402-7627-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,22 +10533,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>70.788.300-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>797.45</v>
+        <v>799.15</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1540-1729-CM26</t>
+          <t>3130-6303-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>873.63</v>
+        <v>867.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1540-1724-CM26</t>
+          <t>1239966-298-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>887.88</v>
+        <v>2194.16</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1540-1725-CM26</t>
+          <t>3263-33-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,22 +10716,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>70.788.300-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>852.3</v>
+        <v>797.45</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1540-1726-CM26</t>
+          <t>1540-1724-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>854.01</v>
+        <v>887.88</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1540-1727-CM26</t>
+          <t>1540-1725-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>837.97</v>
+        <v>852.3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1540-1728-CM26</t>
+          <t>1540-1726-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2660.12</v>
+        <v>854.01</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1057402-7805-CM26</t>
+          <t>1540-1727-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1023.32</v>
+        <v>837.97</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057402-8704-CM26</t>
+          <t>1540-1728-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11016,27 +11016,27 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>59.106.780-k</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1325.78</v>
+        <v>2660.12</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057402-9247-CM26</t>
+          <t>1540-1729-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,6 +11122,189 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
+        <v>873.63</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1057402-7805-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>1023.32</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1057402-8704-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>GLOBAL HEALTHCARE CHILE L P OFICINA DE REPRESENTACION EN CHILE</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>59.106.780-k</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>1325.78</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1057402-9247-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>COMERCIAL LBF LIMITADA</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
         <v>1965.28</v>
       </c>
     </row>
